--- a/card_status_tnga.xlsx
+++ b/card_status_tnga.xlsx
@@ -8,11 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Engine Assembly" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Block" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Crank" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Machining" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Pending Cards" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Block" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ASSEMBLY (MK)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ASSEMBLY" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Crank" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assembly-2 MK1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ASSEMBLY (HEAD SUB)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Piston Sub" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Check new" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Check" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Pending Cards" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,11 +474,11 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Engine Assembly</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -482,32 +487,32 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>ASSEMBLY (MK)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Crank</t>
+          <t>ASSEMBLY</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -526,11 +531,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Machining</t>
+          <t>Crank</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -539,117 +544,102 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Summary of card raised in TNGA (Yesterday)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>LINE</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>INPROGRESS</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Engine Assembly</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (HEAD SUB)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Check new</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
+      <c r="D10" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Crank</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Machining</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
+      <c r="E11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -657,7 +647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -676,7 +666,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Summary of card raised in TNGA Engine Assembly LINE (last 30 days)</t>
+          <t>Summary of card raised in TNGA Check LINE (last 30 days)</t>
         </is>
       </c>
     </row>
@@ -710,7 +700,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Final Product Inspection (FPI)</t>
+          <t>CHK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -720,16 +710,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>issue</t>
+          <t>daily status id</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +727,7455 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E277"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Details For Pending Cards for more than 30 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Process No</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>CheckItem Id</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Pending Since(entryDates)</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Crank</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>62ff383096601d11f3bc202d</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Crank</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OP40</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>62ff383096601d11f3bc203c</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1/1 M</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Crank</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OP140</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>62ff383096601d11f3bc2149</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e40613</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OP50</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e40628</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1/Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OP50</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e4062a</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1/Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OP100A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e406ee</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OP100B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e40706</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1/6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OP100B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e4070b</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OP100B</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e40713</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1/6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OP110A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e40724</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1/3M</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OP120A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e4075e</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1/6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OP120A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e40764</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1/6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OP150B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e407e9</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1/2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>OP210</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>62ff384136c511f680e408b1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1/Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TIAS310</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f6ea</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1/3M</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TIBE316</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f6ff</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TIBE318</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f708</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TIPU305</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f70e</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TIPU305</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f70f</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TIPU305</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f710</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TIPU305</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f711</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TIPU305</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f713</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TIBE318</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f714</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TIBE318</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f71d</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (BLOCK SUB)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TIBE318</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f71e</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (HEAD SUB)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TITM311</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f7bd</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ASSEMBLY (MK)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TIBE328-6-1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>63661b02ce31c7fba477f8b6</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1/6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301ada</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301adb</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301adc</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301add</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301ade</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301adf</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301ae0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301ae1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301ae2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301aee</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301af0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301af5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301af8</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301af9</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301afa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301afb</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301afc</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301afd</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b10</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b11</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b19</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b1a</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b1b</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b1c</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b1d</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b1e</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b1f</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b20</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b21</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Assembly-3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>6455e7b9c533638fe2301b23</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Once/Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>100B</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850b19</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>110A</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850b2f</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>110B</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850b45</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>120A</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850b5b</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>120B</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850b70</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 150B</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bcc</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 150B</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bce</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 150B</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bcf</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 150B</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bd0</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 150B</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bd1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 150B</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bd2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bd6</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bd7</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bd8</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bd9</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bda</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bdb</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bdc</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bdd</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bde</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850bdf</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>160 A</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850be0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>170 A</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c0c</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>170 B</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c21</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>180 A</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c37</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>180 B</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c4c</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c54</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c55</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c56</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c57</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c59</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c5a</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c5b</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c5c</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c5d</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c5f</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c60</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c61</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c62</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c63</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OP20</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c64</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OP210</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c72</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>OP210</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c73</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>OP210</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c7b</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OP210</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c7c</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>OP210</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c7d</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OP210</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c7e</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>OP230</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850c8b</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>OP240</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850ca1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OP250</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850cb7</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OP260</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850ccd</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d1d</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d1e</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d1f</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d20</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d21</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OP30</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d22</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OP55</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d89</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>OP55</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850d8a</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>80A</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850dab</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>80A</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850dac</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>80A</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850dad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TNGA Head</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>80B</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>64af805cea70563f1b850dc1</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>64ba623bbdb6ae732b6be91c</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1/3 M</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e0e0</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e0e2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e0e3</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e0e5</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e0e6</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e0e9</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e0f9</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e100</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e12a</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e12b</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e12e</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e13d</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e140</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e141</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e144</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e145</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TNGA CRANK</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>6548721af05383fe4162e169</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a49d</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a49e</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a49f</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4a0</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4a1</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4a2</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4a3</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4a4</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4a8</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1/3M</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4b8</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4b9</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ba</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4bb</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4be</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ca</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4cd</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ce</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>195 A</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4d4</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>195 A</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4d5</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>195 A</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4d6</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>195 A</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4d7</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>195 A</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4d8</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>195 A</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4d9</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>195 A</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4da</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>195 B</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ea</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>195 B</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4eb</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>195 B</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ec</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>195 B</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ed</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>195 B</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ee</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>195 B</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4ef</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>195 B</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a4f0</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a518</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a519</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a51a</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>TNGA BLOCK</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>655c59cb141a8eb97496a526</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>BS-5</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce70</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>BS-5</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce71</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>BS-5</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce72</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Head Sub</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce99</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Head Sub</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce9a</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Head Sub</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce9b</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Head Sub</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce9c</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>HS-2</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce9d</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HS-2</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce9e</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HS-2</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bce9f</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HS-2</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea0</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>HS-2</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea1</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HS-2</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea2</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HS-2</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea3</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea4</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea5</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea6</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea7</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcea8</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Head Sub</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bceac</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Head Sub</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcead</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>BS-9</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bceb7</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>BS-9</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcebb</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>BS-9</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcec0</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>BS-9</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcec1</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BS-1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcecf</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>BS-1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bced0</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf08</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf1b</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf1c</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf1d</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf1e</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HS-4</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf20</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>TNGA HEAD SUB</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf26</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf2e</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf2f</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf30</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf31</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf38</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf41</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf43</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf45</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>BS-4</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf52</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>BS-4</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf53</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>BS-4</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf54</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>BS-4</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf55</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf57</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>PS-2</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf5d</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>PS-2</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf5f</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>PS-2</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf61</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>1/W</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>PS-2</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf63</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>PS-2</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf64</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>PS-3</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf67</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PS-3</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf68</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>PS-3</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf69</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>PS-1</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf6c</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PS-1</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf6e</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Piston Sub</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>PS-1</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf6f</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>BS-4</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf71</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf74</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf75</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf7e</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf83</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>655da7f10971852d662bcf84</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>1/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>TNGA Block sub</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>BS-2</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>655ed5d4cdc4ed56a24db981</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>MK-1</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d413</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>MK-1</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d414</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>MK-1</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d415</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>MK-1</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d417</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>MK-1</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d418</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>1/1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d419</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d41a</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d41b</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d41c</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d41d</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d41e</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d41f</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>MK-2</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d420</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>MK1-8</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d472</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>MK1-8</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d473</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>MK1-8</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d474</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>MK1-8</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d475</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>MK1-8</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d476</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>MK1-8</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d477</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>MK1-8</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d478</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>1/1W</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK2</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>MK 24</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d481</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK2</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>MK 24</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d482</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK2</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>MK 24</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d483</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK2</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>MK 24</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d484</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>DAily</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Test Bench</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Test Bench(EI-1)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>65697929489adbe5f6c4d49b</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>1/1 D</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>OP250B</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>656eddabcdc4ed56a24e44bc</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>1/1M</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>OP200</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>66440ad1a9cebfcd88cd3e49</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>OP10</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>664fa9b6f6423347561e996b</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>1/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Dummy 30 Jul 2024</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>66a8cb60cae1fe5500f055d7</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>66ac1a44cae1fe5500f09232</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>66ac1a7ecae1fe5500f09235</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>MK-5</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>66c6da1a80614e1d316e4117</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>MK-5</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>66c71e0113d806714ca34487</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>MK-5</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>66c723b113d806714ca34626</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Assembly-2 MK1</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>MK-5</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>66c723e913d806714ca34628</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Test11</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>66cec35258e5ad3b475780d9</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2024-10-02T07:37:43.540Z</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -790,7 +8228,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -800,22 +8238,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>something wrong</t>
+          <t>another</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Dummy 30 Jul 2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -825,16 +8263,96 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>some error</t>
+          <t>achecld</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Summary of card raised in TNGA ASSEMBLY (MK) LINE (last 30 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OP No.</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Abnormality</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Pending Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TITM315</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>checking</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +8379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Summary of card raised in TNGA Crank LINE (last 30 days)</t>
+          <t>Summary of card raised in TNGA ASSEMBLY LINE (last 30 days)</t>
         </is>
       </c>
     </row>
@@ -895,7 +8413,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>TIBE323</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -905,16 +8423,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>issue</t>
+          <t>checking</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -923,6 +8441,111 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Summary of card raised in TNGA Crank LINE (last 30 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OP No.</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Abnormality</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Pending Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OP150</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ccc</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OP105</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -941,7 +8564,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Summary of card raised in TNGA Machining LINE (last 30 days)</t>
+          <t>Summary of card raised in TNGA Assembly-2 MK1 LINE (last 30 days)</t>
         </is>
       </c>
     </row>
@@ -975,7 +8598,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machining Station (M/S)</t>
+          <t>MK-5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -985,16 +8608,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>making it pending</t>
+          <t>checking</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1002,14 +8625,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1021,62 +8644,270 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Details For Pending Cards for more than 30 days</t>
+          <t>Summary of card raised in TNGA ASSEMBLY (HEAD SUB) LINE (last 30 days)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>OP No.</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Process No</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>CheckItem Id</t>
+          <t>Abnormality</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Pending Since(entryDates)</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Pending Days</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crank</t>
+          <t>TIAS334</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OP02</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62ff383096601d11f3bc1fd7</t>
+          <t>ceck</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-07-03T10:09:57.935Z</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1/6M</t>
-        </is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Summary of card raised in TNGA Piston Sub LINE (last 30 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OP No.</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Abnormality</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Pending Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PS-3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>vvvvvv</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PS-2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>decison pending</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Summary of card raised in TNGA Check new LINE (last 30 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OP No.</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Abnormality</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Pending Days</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CHKNEW</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11 12 13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>qqqqqqqqqqqqqqqwertyui</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
